--- a/assets/data/excel/gachaItems.xlsx
+++ b/assets/data/excel/gachaItems.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C93"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,24 +453,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>卡牌ID</t>
+          <t>融合姬卡ID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>卡池ID</t>
+          <t>所属卡池ID</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>权重</t>
+          <t>抽取权重</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MC_N_water_tank_01</t>
+          <t>FM001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MC_N_water_dps_02</t>
+          <t>FM002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -494,13 +494,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MC_N_water_support_03</t>
+          <t>FM003</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -509,13 +509,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MC_N_fire_tank_01</t>
+          <t>FM004</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MC_N_fire_dps_02</t>
+          <t>FM005</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -539,13 +539,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MC_N_fire_support_03</t>
+          <t>FM006</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MC_N_wind_tank_01</t>
+          <t>FM007</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MC_N_wind_dps_02</t>
+          <t>FM008</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MC_N_wind_support_03</t>
+          <t>FM009</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MC_N_light_tank_01</t>
+          <t>FM010</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MC_N_light_dps_02</t>
+          <t>FM011</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -629,13 +629,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MC_N_light_support_03</t>
+          <t>FM012</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MC_N_dark_tank_01</t>
+          <t>FM013</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MC_N_dark_dps_02</t>
+          <t>FM014</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MC_N_dark_support_03</t>
+          <t>FM015</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MC_R_water_tank_01</t>
+          <t>FM016</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -710,7 +710,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MC_R_water_dps_02</t>
+          <t>FM017</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MC_R_water_support_03</t>
+          <t>FM021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -734,13 +734,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>500</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MC_R_fire_tank_01</t>
+          <t>FM022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MC_R_fire_dps_02</t>
+          <t>FM023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -764,13 +764,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MC_R_fire_support_03</t>
+          <t>FM024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -779,13 +779,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MC_R_wind_tank_01</t>
+          <t>FM025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -794,13 +794,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MC_R_wind_dps_02</t>
+          <t>FM026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MC_R_wind_support_03</t>
+          <t>FM027</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MC_R_light_tank_01</t>
+          <t>FM028</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MC_R_light_dps_02</t>
+          <t>FM029</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -854,13 +854,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MC_R_light_support_03</t>
+          <t>FM030</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -869,13 +869,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MC_R_dark_tank_01</t>
+          <t>FM031</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MC_R_dark_dps_02</t>
+          <t>FM032</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MC_R_dark_support_03</t>
+          <t>FM033</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -914,13 +914,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MC_SR_water_tank_01</t>
+          <t>FM034</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -935,7 +935,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MC_SR_water_dps_02</t>
+          <t>FM035</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -950,7 +950,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MC_SR_water_support_03</t>
+          <t>FM036</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MC_SR_fire_tank_01</t>
+          <t>FM037</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MC_SR_fire_dps_02</t>
+          <t>FM038</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MC_SR_fire_support_03</t>
+          <t>FM039</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1004,13 +1004,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MC_SR_wind_tank_01</t>
+          <t>FM041</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>300</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MC_SR_wind_dps_02</t>
+          <t>FM042</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1034,13 +1034,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>300</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MC_SR_wind_support_03</t>
+          <t>FM043</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1049,13 +1049,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>300</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MC_SR_light_tank_01</t>
+          <t>FM044</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>300</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MC_SR_light_dps_02</t>
+          <t>FM045</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>300</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MC_SR_light_support_03</t>
+          <t>FM046</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MC_SR_dark_tank_01</t>
+          <t>FM047</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1109,13 +1109,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MC_SR_dark_dps_02</t>
+          <t>FM048</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MC_SR_dark_support_03</t>
+          <t>FM049</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1139,13 +1139,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MC_SSR_water_tank_01</t>
+          <t>FM050</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1160,7 +1160,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MC_SSR_water_dps_02</t>
+          <t>FM051</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MC_SSR_water_support_03</t>
+          <t>FM052</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1184,13 +1184,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MC_SSR_fire_tank_01</t>
+          <t>FM053</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MC_SSR_fire_dps_02</t>
+          <t>FM054</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1214,13 +1214,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MC_SSR_fire_support_03</t>
+          <t>FM055</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MC_SSR_wind_tank_01</t>
+          <t>FM056</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MC_SSR_wind_dps_02</t>
+          <t>FM057</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1259,13 +1259,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MC_SSR_wind_support_03</t>
+          <t>FM058</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MC_SSR_light_tank_01</t>
+          <t>FM061</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1289,13 +1289,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MC_SSR_light_dps_02</t>
+          <t>FM062</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1304,13 +1304,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MC_SSR_light_support_03</t>
+          <t>FM063</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MC_SSR_dark_tank_01</t>
+          <t>FM064</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MC_SSR_dark_dps_02</t>
+          <t>FM065</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MC_SSR_dark_support_03</t>
+          <t>FM066</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1370,7 +1370,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MC_UR_water_tank_01</t>
+          <t>FM067</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MC_UR_water_dps_02</t>
+          <t>FM068</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MC_UR_water_support_03</t>
+          <t>FM069</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MC_UR_fire_tank_01</t>
+          <t>FM070</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1424,13 +1424,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MC_UR_fire_dps_02</t>
+          <t>FM071</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1439,13 +1439,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MC_UR_fire_support_03</t>
+          <t>FM072</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1454,13 +1454,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MC_UR_wind_tank_01</t>
+          <t>FM073</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MC_UR_wind_dps_02</t>
+          <t>FM074</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MC_UR_wind_support_03</t>
+          <t>FM075</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MC_UR_light_tank_01</t>
+          <t>FM076</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MC_UR_light_dps_02</t>
+          <t>FM077</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MC_UR_light_support_03</t>
+          <t>FM078</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1544,13 +1544,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MC_UR_dark_tank_01</t>
+          <t>FM081</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1559,13 +1559,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MC_UR_dark_dps_02</t>
+          <t>FM082</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1580,7 +1580,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MC_UR_dark_support_03</t>
+          <t>FM083</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MC_LE_water_tank_01</t>
+          <t>FM084</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1604,13 +1604,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MC_LE_water_dps_02</t>
+          <t>FM085</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MC_LE_water_support_03</t>
+          <t>FM086</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1634,13 +1634,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MC_LE_fire_tank_01</t>
+          <t>FM087</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1649,13 +1649,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MC_LE_fire_dps_02</t>
+          <t>FM088</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1664,13 +1664,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MC_LE_fire_support_03</t>
+          <t>FM089</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MC_LE_wind_tank_01</t>
+          <t>FM090</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MC_LE_wind_dps_02</t>
+          <t>FM091</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MC_LE_wind_support_03</t>
+          <t>FM092</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1724,13 +1724,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MC_LE_light_tank_01</t>
+          <t>FM093</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1739,13 +1739,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MC_LE_light_dps_02</t>
+          <t>FM094</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1754,13 +1754,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MC_LE_light_support_03</t>
+          <t>FM095</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MC_LE_dark_tank_01</t>
+          <t>FM096</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1784,37 +1784,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>MC_LE_dark_dps_02</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>POOL_NORMAL</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>MC_LE_dark_support_03</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>POOL_NORMAL</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/excel/gachaItems.xlsx
+++ b/assets/data/excel/gachaItems.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FM001</t>
+          <t>MC_wind_dps_002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FM002</t>
+          <t>MC_dark_dps_003</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -494,13 +494,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FM003</t>
+          <t>MC_water_tank_004</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -509,13 +509,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FM004</t>
+          <t>MC_light_support_005</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FM005</t>
+          <t>MC_light_support_006</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -539,13 +539,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FM006</t>
+          <t>MC_wind_dps_007</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FM007</t>
+          <t>MC_water_tank_008</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FM008</t>
+          <t>MC_dark_support_009</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FM009</t>
+          <t>MC_fire_tank_010</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FM010</t>
+          <t>MC_wind_dps_011</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FM011</t>
+          <t>MC_water_tank_012</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -629,13 +629,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FM012</t>
+          <t>MC_dark_support_013</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FM013</t>
+          <t>MC_wind_tank_014</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FM014</t>
+          <t>MC_wind_dps_015</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>300</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FM015</t>
+          <t>MC_water_support_016</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>500</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FM016</t>
+          <t>MC_wind_dps_017</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -704,13 +704,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>500</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FM017</t>
+          <t>MC_fire_tank_022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FM021</t>
+          <t>MC_wind_dps_023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -734,13 +734,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FM022</t>
+          <t>MC_water_support_024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FM023</t>
+          <t>MC_fire_tank_025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -764,13 +764,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FM024</t>
+          <t>MC_dark_dps_026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -779,13 +779,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FM025</t>
+          <t>MC_fire_dps_027</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -794,13 +794,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FM026</t>
+          <t>MC_water_dps_028</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FM027</t>
+          <t>MC_fire_tank_029</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FM028</t>
+          <t>MC_wind_support_030</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FM029</t>
+          <t>MC_dark_tank_031</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -854,13 +854,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FM030</t>
+          <t>MC_dark_dps_032</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -869,13 +869,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FM031</t>
+          <t>MC_light_support_033</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FM032</t>
+          <t>MC_wind_dps_034</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FM033</t>
+          <t>MC_dark_dps_035</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -914,13 +914,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FM034</t>
+          <t>MC_light_support_036</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>300</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FM035</t>
+          <t>MC_water_support_037</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>300</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FM036</t>
+          <t>MC_fire_tank_038</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>500</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FM037</t>
+          <t>MC_wind_support_039</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FM038</t>
+          <t>MC_fire_tank_042</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FM039</t>
+          <t>MC_wind_support_043</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1004,13 +1004,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FM041</t>
+          <t>MC_water_support_044</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FM042</t>
+          <t>MC_fire_dps_045</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1034,13 +1034,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FM043</t>
+          <t>MC_wind_support_046</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1049,13 +1049,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FM044</t>
+          <t>MC_dark_dps_047</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FM045</t>
+          <t>MC_fire_dps_048</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FM046</t>
+          <t>MC_water_support_049</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FM047</t>
+          <t>MC_light_tank_050</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1109,13 +1109,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FM048</t>
+          <t>MC_fire_dps_051</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FM049</t>
+          <t>MC_light_tank_052</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1139,13 +1139,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FM050</t>
+          <t>MC_wind_dps_053</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FM051</t>
+          <t>MC_water_support_054</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FM052</t>
+          <t>MC_fire_tank_055</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1184,13 +1184,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FM053</t>
+          <t>MC_light_support_056</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>300</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FM054</t>
+          <t>MC_wind_dps_057</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1214,13 +1214,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>300</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FM055</t>
+          <t>MC_water_support_058</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>300</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FM056</t>
+          <t>MC_wind_dps_062</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FM057</t>
+          <t>MC_water_support_063</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1259,13 +1259,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FM058</t>
+          <t>MC_light_support_064</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FM061</t>
+          <t>MC_dark_dps_065</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1289,13 +1289,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FM062</t>
+          <t>MC_fire_tank_066</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1304,13 +1304,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FM063</t>
+          <t>MC_water_tank_067</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FM064</t>
+          <t>MC_wind_dps_068</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FM065</t>
+          <t>MC_light_support_069</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FM066</t>
+          <t>MC_dark_support_070</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1364,13 +1364,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FM067</t>
+          <t>MC_wind_support_071</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FM068</t>
+          <t>MC_fire_dps_072</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FM069</t>
+          <t>MC_water_tank_073</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FM070</t>
+          <t>MC_wind_dps_074</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1424,13 +1424,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FM071</t>
+          <t>MC_light_dps_075</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1439,13 +1439,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FM072</t>
+          <t>MC_wind_tank_076</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1454,13 +1454,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>300</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FM073</t>
+          <t>MC_light_support_077</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>300</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FM074</t>
+          <t>MC_dark_dps_078</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>300</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FM075</t>
+          <t>MC_wind_tank_082</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FM076</t>
+          <t>MC_fire_dps_083</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FM077</t>
+          <t>MC_water_tank_084</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FM078</t>
+          <t>MC_light_support_085</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1544,13 +1544,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FM081</t>
+          <t>MC_fire_tank_086</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1559,13 +1559,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FM082</t>
+          <t>MC_wind_dps_087</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FM083</t>
+          <t>MC_dark_support_088</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>40</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FM084</t>
+          <t>MC_fire_tank_089</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1604,13 +1604,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FM085</t>
+          <t>MC_dark_dps_090</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FM086</t>
+          <t>MC_fire_dps_091</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1634,13 +1634,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FM087</t>
+          <t>MC_light_dps_092</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1649,13 +1649,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FM088</t>
+          <t>MC_dark_tank_093</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1664,13 +1664,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FM089</t>
+          <t>MC_light_support_094</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>300</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FM090</t>
+          <t>MC_fire_tank_095</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>300</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FM091</t>
+          <t>MC_wind_dps_096</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1709,82 +1709,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>FM092</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>POOL_NORMAL</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>FM093</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>POOL_NORMAL</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>FM094</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>POOL_NORMAL</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>FM095</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>POOL_NORMAL</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>FM096</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>POOL_NORMAL</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>500</v>
+        <v>8500</v>
       </c>
     </row>
   </sheetData>
